--- a/outputs/daily/hr_rankings_2026-06-23_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-23_full.xlsx
@@ -2506,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8110,34 +8106,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8394,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9798,34 +9786,30 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12006,34 +11990,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18082,34 +18062,30 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20058,34 +20034,30 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23426,34 +23398,30 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -23710,34 +23678,30 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -28174,34 +28138,30 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -31544,28 +31504,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr"/>
-      <c r="X112" t="inlineStr"/>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y112" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41554,34 +41518,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -51278,34 +51238,30 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -53794,34 +53750,30 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB192" t="inlineStr"/>
       <c r="AC192" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -56560,28 +56512,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W202" t="inlineStr"/>
-      <c r="X202" t="inlineStr"/>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y202" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57406,34 +57362,30 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z205" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB205" t="inlineStr"/>
       <c r="AC205" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -60474,34 +60426,30 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X216" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z216" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X216" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y216" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB216" t="inlineStr"/>
       <c r="AC216" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -66542,34 +66490,30 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X238" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z238" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X238" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75448,34 +75392,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
